--- a/InputData/elec/WUbPPT/Water Use by Power Plant Type.xlsx
+++ b/InputData/elec/WUbPPT/Water Use by Power Plant Type.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28412"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\WUbPPT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\WUbPPT\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABAB2E8-C7B5-485C-A73C-3C2E68CFD24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13500"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -20,17 +21,109 @@
     <sheet name="WUbPPT-withdrawals" sheetId="6" r:id="rId6"/>
     <sheet name="WUbPPT-consumption" sheetId="8" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="96">
+  <si>
+    <t>WUbPPT Water Use by Power Plant Type</t>
+  </si>
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>Joint Global Change Research Institute / Pacific Northwest National Laboratory</t>
+  </si>
+  <si>
+    <t>GCAM model v5.1.2</t>
+  </si>
+  <si>
+    <t>http://www.globalchange.umd.edu/gcam/</t>
+  </si>
+  <si>
+    <t>Reference scenario, energy &gt; energy transformation &gt; electricity &gt; elec gen by gen tech, elec water withdrawals by gen tech, elec water consumption by gen tech</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>GCAM has data for water withdrawals (water taken to use for cooling) and</t>
+  </si>
+  <si>
+    <t>for water consumption (water taken and not returned to the water body -</t>
+  </si>
+  <si>
+    <t>i.e. evaporated).  Most power plant cooling water is discharged back to</t>
+  </si>
+  <si>
+    <t>the water body at a higher temperature, which is why withdrawals are</t>
+  </si>
+  <si>
+    <t>much larger than consumption.</t>
+  </si>
+  <si>
+    <t>For hydroelectric plants, GCAM has no value for withdrawals, but has</t>
+  </si>
+  <si>
+    <t>a value for consumption.  We assume the consumption value is</t>
+  </si>
+  <si>
+    <t>the amount of water that evaporates off the surface of the reservoir</t>
+  </si>
+  <si>
+    <t>created by the dam, which otherwise would not have had a chance</t>
+  </si>
+  <si>
+    <t>to evaporate before flowing downriver.  We assume it has no water</t>
+  </si>
+  <si>
+    <t>withdrawals because the reservoir is considered a part of the</t>
+  </si>
+  <si>
+    <t>water system.</t>
+  </si>
+  <si>
+    <t>Conversion Factors</t>
+  </si>
+  <si>
+    <t>liters per cubic km</t>
+  </si>
+  <si>
+    <t>MWh per EJ</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>subsector</t>
+  </si>
+  <si>
+    <t>technology</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
   <si>
     <t>Reference,date=2018-28-11T14:16:43-08:00</t>
   </si>
@@ -38,135 +131,120 @@
     <t>USA</t>
   </si>
   <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>biomass (IGCC)</t>
+  </si>
+  <si>
+    <t>EJ</t>
+  </si>
+  <si>
+    <t>biomass (conv)</t>
+  </si>
+  <si>
+    <t>biomass cogen</t>
+  </si>
+  <si>
+    <t>coal</t>
+  </si>
+  <si>
+    <t>coal (IGCC)</t>
+  </si>
+  <si>
+    <t>coal (conv pul)</t>
+  </si>
+  <si>
+    <t>coal cogen</t>
+  </si>
+  <si>
+    <t>gas</t>
+  </si>
+  <si>
+    <t>gas (CC)</t>
+  </si>
+  <si>
+    <t>gas (steam/CT)</t>
+  </si>
+  <si>
+    <t>gas cogen</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>hydrogen</t>
+  </si>
+  <si>
+    <t>hydrogen cogen</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>Gen_III</t>
+  </si>
+  <si>
+    <t>Gen_II_LWR</t>
+  </si>
+  <si>
+    <t>refined liquids</t>
+  </si>
+  <si>
+    <t>refined liquids (CC)</t>
+  </si>
+  <si>
+    <t>refined liquids (steam/CT)</t>
+  </si>
+  <si>
+    <t>refined liquids cogen</t>
+  </si>
+  <si>
+    <t>rooftop_pv</t>
+  </si>
+  <si>
+    <t>solar</t>
+  </si>
+  <si>
+    <t>CSP</t>
+  </si>
+  <si>
+    <t>CSP_storage</t>
+  </si>
+  <si>
+    <t>PV</t>
+  </si>
+  <si>
+    <t>PV_storage</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>wind_storage</t>
+  </si>
+  <si>
+    <t>sector</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
     <t>electricity</t>
   </si>
   <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t>biomass (IGCC)</t>
-  </si>
-  <si>
     <t>water_td_elec_W</t>
   </si>
   <si>
     <t>km^3</t>
   </si>
   <si>
-    <t>biomass (conv)</t>
-  </si>
-  <si>
-    <t>coal</t>
-  </si>
-  <si>
-    <t>coal (IGCC)</t>
-  </si>
-  <si>
-    <t>coal (conv pul)</t>
-  </si>
-  <si>
-    <t>gas</t>
-  </si>
-  <si>
-    <t>gas (CC)</t>
-  </si>
-  <si>
-    <t>gas (steam/CT)</t>
-  </si>
-  <si>
-    <t>geothermal</t>
-  </si>
-  <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>Gen_III</t>
-  </si>
-  <si>
-    <t>Gen_II_LWR</t>
-  </si>
-  <si>
-    <t>refined liquids</t>
-  </si>
-  <si>
-    <t>refined liquids (CC)</t>
-  </si>
-  <si>
-    <t>refined liquids (steam/CT)</t>
-  </si>
-  <si>
-    <t>solar</t>
-  </si>
-  <si>
-    <t>CSP</t>
-  </si>
-  <si>
-    <t>CSP_storage</t>
-  </si>
-  <si>
-    <t>PV</t>
-  </si>
-  <si>
-    <t>PV_storage</t>
-  </si>
-  <si>
     <t>water_td_elec_C</t>
   </si>
   <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>EJ</t>
-  </si>
-  <si>
-    <t>biomass cogen</t>
-  </si>
-  <si>
-    <t>coal cogen</t>
-  </si>
-  <si>
-    <t>gas cogen</t>
-  </si>
-  <si>
-    <t>hydrogen</t>
-  </si>
-  <si>
-    <t>hydrogen cogen</t>
-  </si>
-  <si>
-    <t>refined liquids cogen</t>
-  </si>
-  <si>
-    <t>rooftop_pv</t>
-  </si>
-  <si>
-    <t>wind</t>
-  </si>
-  <si>
-    <t>wind_storage</t>
-  </si>
-  <si>
-    <t>scenario</t>
-  </si>
-  <si>
-    <t>region</t>
-  </si>
-  <si>
-    <t>subsector</t>
-  </si>
-  <si>
-    <t>technology</t>
-  </si>
-  <si>
-    <t>Units</t>
-  </si>
-  <si>
-    <t>sector</t>
-  </si>
-  <si>
-    <t>input</t>
-  </si>
-  <si>
     <t>Generation (EJ)</t>
   </si>
   <si>
@@ -182,46 +260,25 @@
     <t>Water Consumption per Unit Generation (km^3/EJ)</t>
   </si>
   <si>
-    <t>Conversion Factors</t>
-  </si>
-  <si>
-    <t>MWh per EJ</t>
-  </si>
-  <si>
     <t>Water Withdrawals per Unit Generation (l/MWh)</t>
   </si>
   <si>
     <t>Water Consumption per Unit Generation (l/MWh)</t>
   </si>
   <si>
-    <t>liters per cubic km</t>
-  </si>
-  <si>
-    <t>WUbPPT Water Use by Power Plant Type</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>GCAM model v5.1.2</t>
-  </si>
-  <si>
-    <t>http://www.globalchange.umd.edu/gcam/</t>
-  </si>
-  <si>
-    <t>Joint Global Change Research Institute / Pacific Northwest National Laboratory</t>
-  </si>
-  <si>
-    <t>Reference scenario, energy &gt; energy transformation &gt; electricity &gt; elec gen by gen tech, elec water withdrawals by gen tech, elec water consumption by gen tech</t>
+    <t>Unit: liters/(MW*hour)</t>
+  </si>
+  <si>
+    <t>Water demand</t>
   </si>
   <si>
     <t>hard coal</t>
   </si>
   <si>
-    <t>natural gas nonpeaker</t>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
   </si>
   <si>
     <t>onshore wind</t>
@@ -245,42 +302,6 @@
     <t>offshore wind</t>
   </si>
   <si>
-    <t>GCAM has data for water withdrawals (water taken to use for cooling) and</t>
-  </si>
-  <si>
-    <t>for water consumption (water taken and not returned to the water body -</t>
-  </si>
-  <si>
-    <t>i.e. evaporated).  Most power plant cooling water is discharged back to</t>
-  </si>
-  <si>
-    <t>the water body at a higher temperature, which is why withdrawals are</t>
-  </si>
-  <si>
-    <t>much larger than consumption.</t>
-  </si>
-  <si>
-    <t>For hydroelectric plants, GCAM has no value for withdrawals, but has</t>
-  </si>
-  <si>
-    <t>a value for consumption.  We assume the consumption value is</t>
-  </si>
-  <si>
-    <t>the amount of water that evaporates off the surface of the reservoir</t>
-  </si>
-  <si>
-    <t>created by the dam, which otherwise would not have had a chance</t>
-  </si>
-  <si>
-    <t>to evaporate before flowing downriver.  We assume it has no water</t>
-  </si>
-  <si>
-    <t>withdrawals because the reservoir is considered a part of the</t>
-  </si>
-  <si>
-    <t>water system.</t>
-  </si>
-  <si>
     <t>crude oil</t>
   </si>
   <si>
@@ -290,17 +311,32 @@
     <t>municipal solid waste</t>
   </si>
   <si>
-    <t>Water withdrawals (liters/(MW*hour))</t>
-  </si>
-  <si>
-    <t>Water consumption (liters/(MW*hour))</t>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
+    <t>hydrogen combustion turbine</t>
+  </si>
+  <si>
+    <t>hydrogen combined cycle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,6 +356,29 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -352,7 +411,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -374,9 +433,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -654,166 +718,166 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" s="7">
         <v>2018</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="B6" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
       <c r="A24" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
       <c r="A26">
         <f>10^12</f>
         <v>1000000000000</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
       <c r="A29">
         <v>277777777.77777702</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z25"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="18.3984375" customWidth="1"/>
-    <col min="4" max="4" width="27.3984375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:26">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E1" s="2">
         <v>1990</v>
@@ -879,21 +943,21 @@
         <v>2100</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -959,21 +1023,21 @@
         <v>0.34978900000000002</v>
       </c>
       <c r="Z2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E3">
         <v>7.9134899999999994E-2</v>
@@ -1039,21 +1103,21 @@
         <v>0.30399399999999999</v>
       </c>
       <c r="Z3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E4">
         <v>0.22271299999999999</v>
@@ -1119,21 +1183,21 @@
         <v>0.187585</v>
       </c>
       <c r="Z4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1</v>
-      </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1199,21 +1263,21 @@
         <v>3.5587300000000002</v>
       </c>
       <c r="Z5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>6.0290900000000001</v>
@@ -1279,21 +1343,21 @@
         <v>10.87</v>
       </c>
       <c r="Z6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1</v>
-      </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>8.9847099999999999E-2</v>
@@ -1359,21 +1423,21 @@
         <v>0.139098</v>
       </c>
       <c r="Z7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1</v>
-      </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E8">
         <v>0.59030000000000005</v>
@@ -1439,21 +1503,21 @@
         <v>4.0196699999999996</v>
       </c>
       <c r="Z8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1</v>
-      </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E9">
         <v>0.43599500000000002</v>
@@ -1519,21 +1583,21 @@
         <v>0.14057500000000001</v>
       </c>
       <c r="Z9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1</v>
-      </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E10">
         <v>0.35644199999999998</v>
@@ -1599,21 +1663,21 @@
         <v>0.30209000000000003</v>
       </c>
       <c r="Z10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1</v>
-      </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="E11">
         <v>5.7645599999999998E-2</v>
@@ -1679,21 +1743,21 @@
         <v>0.71600299999999995</v>
       </c>
       <c r="Z11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E12">
         <v>0.98334699999999997</v>
@@ -1759,21 +1823,21 @@
         <v>1.04634</v>
       </c>
       <c r="Z12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1</v>
-      </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1839,21 +1903,21 @@
         <v>3.14831E-2</v>
       </c>
       <c r="Z13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1</v>
-      </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1919,21 +1983,21 @@
         <v>4.0533299999999999</v>
       </c>
       <c r="Z14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1</v>
-      </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E15">
         <v>2.20139</v>
@@ -1999,21 +2063,21 @@
         <v>0</v>
       </c>
       <c r="Z15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1</v>
-      </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2079,21 +2143,21 @@
         <v>0.122679</v>
       </c>
       <c r="Z16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1</v>
-      </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E17">
         <v>0.45076699999999997</v>
@@ -2159,21 +2223,21 @@
         <v>5.2327800000000002E-3</v>
       </c>
       <c r="Z17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1</v>
-      </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E18">
         <v>1.9592499999999999E-2</v>
@@ -2239,21 +2303,21 @@
         <v>3.0210399999999998E-2</v>
       </c>
       <c r="Z18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1</v>
-      </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2319,21 +2383,21 @@
         <v>5.0576799999999998E-2</v>
       </c>
       <c r="Z19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1</v>
-      </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E20">
         <v>2.3869E-3</v>
@@ -2399,21 +2463,21 @@
         <v>2.7512399999999999E-2</v>
       </c>
       <c r="Z20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1</v>
-      </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2479,21 +2543,21 @@
         <v>0.30076000000000003</v>
       </c>
       <c r="Z21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1</v>
-      </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="E22" s="1">
         <v>1.0800400000000001E-5</v>
@@ -2559,21 +2623,21 @@
         <v>0.49257239999999902</v>
       </c>
       <c r="Z22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1</v>
-      </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2639,21 +2703,21 @@
         <v>4.4284629999999997E-3</v>
       </c>
       <c r="Z23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1</v>
-      </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E24">
         <v>1.10381E-2</v>
@@ -2719,21 +2783,21 @@
         <v>2.8700709999999998</v>
       </c>
       <c r="Z24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1</v>
-      </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2799,7 +2863,7 @@
         <v>1.6823399999999999E-2</v>
       </c>
       <c r="Z25" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2808,34 +2872,34 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" customWidth="1"/>
-    <col min="3" max="3" width="12.73046875" customWidth="1"/>
-    <col min="4" max="4" width="15.59765625" customWidth="1"/>
-    <col min="5" max="5" width="29.265625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="29.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:28">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="G1" s="2">
         <v>1990</v>
@@ -2901,27 +2965,27 @@
         <v>2100</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2987,27 +3051,27 @@
         <v>0.12786110199999901</v>
       </c>
       <c r="AB2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>0.69392854000000004</v>
@@ -3073,27 +3137,27 @@
         <v>0.15418430999999999</v>
       </c>
       <c r="AB3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3159,27 +3223,27 @@
         <v>1.3248231829999999</v>
       </c>
       <c r="AB4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>110.27552193</v>
@@ -3245,27 +3309,27 @@
         <v>25.970151419999901</v>
       </c>
       <c r="AB5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
       <c r="A6" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G6">
         <v>0.67783796999999901</v>
@@ -3331,27 +3395,27 @@
         <v>1.2859827099999901</v>
       </c>
       <c r="AB6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
       <c r="A7" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G7">
         <v>3.8073925999999898</v>
@@ -3417,27 +3481,27 @@
         <v>6.2147147999999999E-2</v>
       </c>
       <c r="AB7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
       <c r="A8" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F8" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>6.9623000000000004E-2</v>
@@ -3503,27 +3567,27 @@
         <v>1.0086651600000001</v>
       </c>
       <c r="AB8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28">
       <c r="A9" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3589,27 +3653,27 @@
         <v>7.1137269999999999</v>
       </c>
       <c r="AB9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28">
       <c r="A10" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F10" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>38.676989999999897</v>
@@ -3675,27 +3739,27 @@
         <v>0</v>
       </c>
       <c r="AB10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28">
       <c r="A11" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3761,27 +3825,27 @@
         <v>1.3921205640000001</v>
       </c>
       <c r="AB11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
       <c r="A12" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F12" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>3.9937057</v>
@@ -3847,27 +3911,27 @@
         <v>3.5751641000000001E-3</v>
       </c>
       <c r="AB12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28">
       <c r="A13" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G13">
         <v>1.33932E-3</v>
@@ -3933,27 +3997,27 @@
         <v>2.52174656782999E-2</v>
       </c>
       <c r="AB13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28">
       <c r="A14" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -4019,27 +4083,27 @@
         <v>0.27567077370999998</v>
       </c>
       <c r="AB14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28">
       <c r="A15" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="F15" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G15" s="1">
         <v>6.0002999999999998E-8</v>
@@ -4105,27 +4169,27 @@
         <v>2.7365339999999901E-3</v>
       </c>
       <c r="AB15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28">
       <c r="A16" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -4191,7 +4255,7 @@
         <v>2.4602769999999999E-5</v>
       </c>
       <c r="AB16" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -4200,34 +4264,34 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AB17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="14.59765625" customWidth="1"/>
-    <col min="4" max="4" width="17.1328125" customWidth="1"/>
-    <col min="5" max="5" width="27.73046875" customWidth="1"/>
-    <col min="6" max="6" width="18.86328125" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="5" max="5" width="27.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:28">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="G1" s="2">
         <v>1990</v>
@@ -4293,27 +4357,27 @@
         <v>2100</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -4379,27 +4443,27 @@
         <v>0.121749522</v>
       </c>
       <c r="AB2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>1.7264350000000001E-2</v>
@@ -4465,27 +4529,27 @@
         <v>9.7061778000000001E-2</v>
       </c>
       <c r="AB3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -4551,27 +4615,27 @@
         <v>1.260898283</v>
       </c>
       <c r="AB4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>3.1418712099999899</v>
@@ -4637,27 +4701,27 @@
         <v>6.9712168400000003</v>
       </c>
       <c r="AB5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
       <c r="A6" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>0.10108934999999999</v>
@@ -4723,27 +4787,27 @@
         <v>0.449319202999999</v>
       </c>
       <c r="AB6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
       <c r="A7" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>8.9163800000000001E-2</v>
@@ -4809,27 +4873,27 @@
         <v>4.1457725000000001E-2</v>
       </c>
       <c r="AB7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
       <c r="A8" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>6.9623000000000004E-2</v>
@@ -4895,27 +4959,27 @@
         <v>1.0086651600000001</v>
       </c>
       <c r="AB8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28">
       <c r="A9" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>4.64358</v>
@@ -4981,27 +5045,27 @@
         <v>4.9410299999999996</v>
       </c>
       <c r="AB9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28">
       <c r="A10" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -5067,27 +5131,27 @@
         <v>2.5219843000000002</v>
       </c>
       <c r="AB10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28">
       <c r="A11" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G11">
         <v>1.0302370000000001</v>
@@ -5153,27 +5217,27 @@
         <v>0</v>
       </c>
       <c r="AB11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
       <c r="A12" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -5239,27 +5303,27 @@
         <v>1.6948847600000001E-2</v>
       </c>
       <c r="AB12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28">
       <c r="A13" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>0.1271708</v>
@@ -5325,27 +5389,27 @@
         <v>2.4593980999999998E-3</v>
       </c>
       <c r="AB13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28">
       <c r="A14" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>1.33932E-3</v>
@@ -5411,27 +5475,27 @@
         <v>2.52174656782999E-2</v>
       </c>
       <c r="AB14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28">
       <c r="A15" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -5497,27 +5561,27 @@
         <v>0.27567077370999998</v>
       </c>
       <c r="AB15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28">
       <c r="A16" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="F16" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G16" s="1">
         <v>6.0002999999999998E-8</v>
@@ -5583,27 +5647,27 @@
         <v>2.7365339999999901E-3</v>
       </c>
       <c r="AB16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28">
       <c r="A17" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -5669,7 +5733,7 @@
         <v>2.4602769999999999E-5</v>
       </c>
       <c r="AB17" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -5679,47 +5743,47 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="18.59765625" customWidth="1"/>
-    <col min="3" max="3" width="27.265625" customWidth="1"/>
-    <col min="4" max="4" width="27.3984375" customWidth="1"/>
-    <col min="5" max="5" width="29.265625" customWidth="1"/>
-    <col min="6" max="8" width="28.59765625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
+    <col min="5" max="5" width="29.28515625" customWidth="1"/>
+    <col min="6" max="8" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" ht="30">
       <c r="A1" s="3" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B2">
         <f>VLOOKUP($A2,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5750,9 +5814,9 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B3">
         <f>VLOOKUP($A3,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5783,9 +5847,9 @@
         <v>971.73432153190504</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <f>VLOOKUP($A4,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5816,9 +5880,9 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <f>VLOOKUP($A5,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5849,9 +5913,9 @@
         <v>1960.1218806510001</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <f>VLOOKUP($A6,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5882,9 +5946,9 @@
         <v>620.64013917559782</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <f>VLOOKUP($A7,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5915,9 +5979,9 @@
         <v>745.03641899418494</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="B8">
         <f>VLOOKUP($A8,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5948,9 +6012,9 @@
         <v>4930.3337614825323</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B9">
         <f>VLOOKUP($A9,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5977,9 +6041,9 @@
         <v>16999.982182329317</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="B10">
         <f>VLOOKUP($A10,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6010,9 +6074,9 @@
         <v>2226.6884419345611</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="B11">
         <f>VLOOKUP($A11,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6043,9 +6107,9 @@
         <v>1684.774202794702</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="B12">
         <f>VLOOKUP($A12,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6076,9 +6140,9 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B13">
         <f>VLOOKUP($A13,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6109,9 +6173,9 @@
         <v>1183.8566612430841</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <f>VLOOKUP($A14,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6142,9 +6206,9 @@
         <v>2103.5281074696754</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="B15">
         <f>VLOOKUP($A15,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6175,9 +6239,9 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="B16">
         <f>VLOOKUP($A16,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6208,9 +6272,9 @@
         <v>20.000187272534593</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="B17">
         <f>VLOOKUP($A17,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6247,162 +6311,477 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
-    <tabColor theme="8" tint="-0.249977111117893"/>
+    <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.265625" customWidth="1"/>
-    <col min="2" max="2" width="18.265625" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2">
+      <c r="A1" s="11" t="s">
+        <v>74</v>
+      </c>
       <c r="B1" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="B2" s="6">
         <f>'2015 Consolidated Data'!G5</f>
         <v>54577.83755331373</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B3" s="6">
+        <f>'2015 Consolidated Data'!G7</f>
+        <v>30331.387156235895</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="6">
         <f>'2015 Consolidated Data'!G6</f>
         <v>4159.9245358989992</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="6">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="6">
         <f>'2015 Consolidated Data'!G11</f>
         <v>63249.562164099065</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="6">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="6">
         <f>'2015 Consolidated Data'!G9</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="6">
+        <v>79</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="6">
         <f>'2015 Consolidated Data'!G16</f>
         <v>20.000187272534593</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="6">
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="6">
         <f>'2015 Consolidated Data'!G14</f>
         <v>2103.5281074696754</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6">
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="6">
         <f>'2015 Consolidated Data'!G3</f>
         <v>13890.685457654999</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="6">
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="6">
         <f>'2015 Consolidated Data'!G8</f>
         <v>4930.3337614825323</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="6">
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="6">
         <f>'2015 Consolidated Data'!G13</f>
         <v>23313.172724314474</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="6">
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="6">
         <f>'2015 Consolidated Data'!G7</f>
         <v>30331.387156235895</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="6">
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="6">
         <f>'2015 Consolidated Data'!G5</f>
         <v>54577.83755331373</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="6">
+        <f>B12</f>
+        <v>23313.172724314474</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="6">
+        <f>B12</f>
+        <v>23313.172724314474</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="6">
+        <f>B10</f>
+        <v>13890.685457654999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="6">
+        <f>B2</f>
+        <v>54577.83755331373</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="6">
+        <f>B4</f>
+        <v>4159.9245358989992</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="6">
+        <f>B10</f>
+        <v>13890.685457654999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="6">
+        <f>B14</f>
+        <v>54577.83755331373</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="6">
+        <f>B5</f>
+        <v>63249.562164099065</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="6">
+        <f>B13</f>
+        <v>30331.387156235895</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="6">
+        <f>B4</f>
+        <v>4159.9245358989992</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <tabColor theme="8" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="6">
+        <f>'2015 Consolidated Data'!H5</f>
+        <v>1960.1218806510001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="6">
+        <f>'2015 Consolidated Data'!H7</f>
+        <v>745.03641899418494</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="6">
+        <f>'2015 Consolidated Data'!H6</f>
+        <v>620.64013917559782</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="6">
+        <f>'2015 Consolidated Data'!H11</f>
+        <v>1684.774202794702</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="6">
+        <f>'2015 Consolidated Data'!H9</f>
+        <v>16999.982182329317</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="6">
+        <f>'2015 Consolidated Data'!H16</f>
+        <v>20.000187272534593</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="6">
+        <f>'2015 Consolidated Data'!H14</f>
+        <v>2103.5281074696754</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="6">
+        <f>'2015 Consolidated Data'!H3</f>
+        <v>971.73432153190504</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="6">
+        <f>'2015 Consolidated Data'!H8</f>
+        <v>4930.3337614825323</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="6">
+        <f>'2015 Consolidated Data'!H13</f>
+        <v>1183.8566612430841</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="6">
+        <f>'2015 Consolidated Data'!H7</f>
+        <v>745.03641899418494</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+        <v>84</v>
+      </c>
+      <c r="B14" s="6">
+        <f>'2015 Consolidated Data'!H5</f>
+        <v>1960.1218806510001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="6">
-        <f>B11</f>
-        <v>23313.172724314474</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B16" s="6">
-        <f>B11</f>
-        <v>23313.172724314474</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+        <f>B12</f>
+        <v>1183.8566612430841</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B17" s="6">
-        <f>B9</f>
-        <v>13890.685457654999</v>
+        <f>B12</f>
+        <v>1183.8566612430841</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="6">
+        <f>B10</f>
+        <v>971.73432153190504</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="6">
+        <f>B2</f>
+        <v>1960.1218806510001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="6">
+        <f>B4</f>
+        <v>620.64013917559782</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="6">
+        <f>B10</f>
+        <v>971.73432153190504</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="6">
+        <f>B14</f>
+        <v>1960.1218806510001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="6">
+        <f>B5</f>
+        <v>1684.774202794702</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="6">
+        <f>B13</f>
+        <v>745.03641899418494</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="6">
+        <f>B4</f>
+        <v>620.64013917559782</v>
       </c>
     </row>
   </sheetData>
@@ -6410,166 +6789,173 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="8" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="24.265625" customWidth="1"/>
-    <col min="2" max="2" width="18.265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B1" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="6">
-        <f>'2015 Consolidated Data'!H5</f>
-        <v>1960.1218806510001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="6">
-        <f>'2015 Consolidated Data'!H6</f>
-        <v>620.64013917559782</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="6">
-        <f>'2015 Consolidated Data'!H11</f>
-        <v>1684.774202794702</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="6">
-        <f>'2015 Consolidated Data'!H9</f>
-        <v>16999.982182329317</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="6">
-        <f>'2015 Consolidated Data'!H16</f>
-        <v>20.000187272534593</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="6">
-        <f>'2015 Consolidated Data'!H14</f>
-        <v>2103.5281074696754</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6">
-        <f>'2015 Consolidated Data'!H3</f>
-        <v>971.73432153190504</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="6">
-        <f>'2015 Consolidated Data'!H8</f>
-        <v>4930.3337614825323</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="6">
-        <f>'2015 Consolidated Data'!H13</f>
-        <v>1183.8566612430841</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="6">
-        <f>'2015 Consolidated Data'!H7</f>
-        <v>745.03641899418494</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="6">
-        <f>'2015 Consolidated Data'!H5</f>
-        <v>1960.1218806510001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="6">
-        <f>B11</f>
-        <v>1183.8566612430841</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="6">
-        <f>B11</f>
-        <v>1183.8566612430841</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="6">
-        <f>B9</f>
-        <v>971.73432153190504</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F7C0388-9374-4CD5-BE21-52AFB15FF294}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C45F9E97-A48B-4C18-A60E-D9F618E8897E}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{138C0B8C-B6D2-43DF-A245-451D8F4E9140}"/>
 </file>